--- a/result/LOXL2_LUSC_Tables.xlsx
+++ b/result/LOXL2_LUSC_Tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,17 +438,18 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -462,6 +464,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -470,14 +473,17 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>85</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>104</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.087</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.143</t>
         </is>
       </c>
     </row>
@@ -488,12 +494,15 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>159</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>139</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -504,346 +513,392 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.173</t>
+        <v>55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.068</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>70</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>189</v>
+      </c>
+      <c r="D7" t="n">
+        <v>173</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>189</v>
-      </c>
-      <c r="C8" t="n">
-        <v>173</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>119</v>
+      </c>
+      <c r="D9" t="n">
+        <v>118</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.650</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>118</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.368</t>
-        </is>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D10" t="n">
+        <v>74</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="D11" t="n">
+        <v>47</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>200</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.526</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>200</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.458</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>159</v>
+      </c>
+      <c r="D17" t="n">
+        <v>151</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>151</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="D18" t="n">
+        <v>61</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="D19" t="n">
+        <v>26</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>46</v>
+      </c>
+      <c r="D22" t="n">
+        <v>62</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.342</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>62</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="D23" t="n">
+        <v>135</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>135</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>12</v>
-      </c>
-      <c r="C26" t="n">
-        <v>11</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>33</v>
+      </c>
+      <c r="D27" t="n">
+        <v>43</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.418</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.261</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
         <v>211</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D28" t="n">
         <v>201</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -856,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,32 +937,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PLAURexpression</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SNAI1expression</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VEGFCexpression</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CDKN2AExpression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SOX2Expression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PIK3CAExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>NOTCH1Expression</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
         </is>
       </c>
     </row>
@@ -929,37 +1004,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>0.564</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.266</t>
+          <t>0.440</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.115</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.065</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.018</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.275</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-0.103</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.077</t>
         </is>
       </c>
     </row>
@@ -967,23 +1062,23 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>0.959</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -993,17 +1088,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.153</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.091</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1135,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1030,32 +1145,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.041</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-0.046</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -1063,50 +1198,70 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>0.959</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.802</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.981</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1116,12 +1271,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.080</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.009</t>
+          <t>0.045</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1131,27 +1286,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>-0.035</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.046</t>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-0.116</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-0.025</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-0.012</t>
         </is>
       </c>
     </row>
@@ -1159,50 +1334,70 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.330</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.970</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.447</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.326</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.788</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.785</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDKN2AExpression</t>
+          <t>ITGB1expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1212,17 +1407,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>0.564</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.023</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,22 +1427,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.390</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>-0.080</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-0.399</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-0.112</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-0.105</t>
         </is>
       </c>
     </row>
@@ -1255,50 +1470,70 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.330</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.013</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOX2Expression</t>
+          <t>PLAURexpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1308,22 +1543,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.266</t>
+          <t>0.440</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.041</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.390</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1333,17 +1568,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.421</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>0.470</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.123</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>0.012</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-0.146</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-0.341</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-0.248</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-0.121</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1606,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1361,17 +1616,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1382,19 +1637,39 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.008</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIK3CAExpression</t>
+          <t>SNAI1expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1404,27 +1679,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.115</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.421</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1434,12 +1709,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.037</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.051</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-0.075</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-0.281</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-0.231</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-0.104</t>
         </is>
       </c>
     </row>
@@ -1447,27 +1742,27 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.970</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1478,19 +1773,39 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.099</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.022</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOTCH1Expression</t>
+          <t>VEGFCexpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1500,32 +1815,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-0.046</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>-0.035</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.470</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.037</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1535,7 +1850,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-0.298</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-0.180</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-0.059</t>
         </is>
       </c>
     </row>
@@ -1543,50 +1878,70 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.447</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.943</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.191</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1596,42 +1951,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.065</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.046</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>-0.080</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.146</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.051</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.058</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0.050</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.196</t>
         </is>
       </c>
     </row>
@@ -1639,45 +2014,609 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>0.811</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CDKN2AExpression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.018</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.075</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.014</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.788</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.807</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.099</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.943</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.929</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0.761</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SOX2Expression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.275</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-0.116</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-0.399</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-0.341</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.281</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.298</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.058</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.415</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.929</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PIK3CAExpression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.103</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-0.025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-0.112</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-0.248</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-0.231</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.180</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.050</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-0.014</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.528</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-0.032</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.717</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.013</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.273</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.761</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NOTCH1Expression</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.077</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-0.105</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-0.121</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-0.104</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.059</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>-0.032</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.091</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.981</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.785</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.020</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.191</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.104</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1690,7 +2629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1706,6 +2645,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1713,15 +2662,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>ageG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.029</t>
+        <v>1.334</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.835</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.076</t>
         </is>
       </c>
     </row>
@@ -1732,86 +2687,105 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.885</t>
+        <v>0.999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.806</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOXL2group_Low</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.016</t>
+        <v>1.205</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>LOXL2group_High</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.163</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.397</t>
+        <v>3039547.802</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.993</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>LOXL2group_Low</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.931</t>
+        <v>2084187.489</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pathologic_stage_3.0</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.384</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.109</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.853</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.025</t>
+        <v>1.159</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.639</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.405</t>
         </is>
       </c>
     </row>
@@ -2757,4 +3731,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LOXL2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.228</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LOXL2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8.811</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>